--- a/solutions.xlsx
+++ b/solutions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\modern-excel-demo-day-america250\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA484DB9-608A-43AE-9E6F-507DE7EC8D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2A08F7-DEC4-45C6-9ED7-CCC1A88D14FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,14 +537,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>37042</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1502833</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>84666</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>119518</xdr:colOff>
+      <xdr:colOff>8393</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>42256</xdr:rowOff>
     </xdr:to>
@@ -574,7 +574,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6037792" y="4402666"/>
+          <a:off x="5926667" y="4402666"/>
           <a:ext cx="5755142" cy="4100965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
